--- a/ig/ch-elm/StructureDefinition-ch-elm-practitioner-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-practitioner-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}ch-pract-1:If a HumanName is provided, at least one HumanName must have a given and family name. {name.where(family.exists() and given.exists()).count()&gt;0 or name.empty()}ch-pract-2:gender unknown is currently not used in Switzerland in eCH and the EPR {gender.empty() or gender!='unknown'}ch-elm-practioner-zsr-check-length:invalid ZSR number, cannot be processed, must be exactly one letter and 6 digits long {identifier.where(system='urn:oid:2.16.756.5.30.1.123.100.2.1.1').exists() implies identifier.where(system='urn:oid:2.16.756.5.30.1.123.100.2.1.1').value.matches('^[A-Z][0-9]{6}$').allTrue()}ch-elm-practioner-zsr-check-digit:invalid ZSR number, cannot be processed, must pass the modulus 26 check - https://confluence.sasis.ch/display/PublicZSR/ZSR+Webservice+FAQ {identifier.where(system='urn:oid:2.16.756.5.30.1.123.100.2.1.1').exists() implies identifier.where(system='urn:oid:2.16.756.5.30.1.123.100.2.1.1').value.select(((substring(1,1).toInteger()*6)+(substring(2,1).toInteger()*5)+(substring(3,1).toInteger()*4)+(substring(4,1).toInteger()*3)+(substring(5,1).toInteger()*2)+(substring(6,1).toInteger()))mod(26)=iif(substring(0,1)='A',1,iif(substring(0,1)='B',2,iif(substring(0,1)='C',3,iif(substring(0,1)='D',4,iif(substring(0,1)='E',5,iif(substring(0,1)='F',6,iif(substring(0,1)='G',7,iif(substring(0,1)='H',8,iif(substring(0,1)='I',9,iif(substring(0,1)='J',10,iif(substring(0,1)='K',11,iif(substring(0,1)='L',12,iif(substring(0,1)='M',13,iif(substring(0,1)='N',14,iif(substring(0,1)='O',15,iif(substring(0,1)='P',16,iif(substring(0,1)='Q',17,iif(substring(0,1)='R',18,iif(substring(0,1)='S',19,iif(substring(0,1)='T',20,iif(substring(0,1)='U',21,iif(substring(0,1)='V',22,iif(substring(0,1)='W',23,iif(substring(0,1)='X',24,iif(substring(0,1)='Y',25,iif(substring(0,1)='Z',26,-1))))))))))))))))))))))))))).allTrue()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}ch-pract-1:If a HumanName is provided, at least one HumanName must have a family name. {name.where(family.exists()).count()&gt;0 or name.empty()}ch-pract-2:gender unknown is currently not used in Switzerland in eCH and the EPR {gender.empty() or gender!='unknown'}ch-elm-practioner-zsr-check-length:invalid ZSR number, cannot be processed, must be exactly one letter and 6 digits long {identifier.where(system='urn:oid:2.16.756.5.30.1.123.100.2.1.1').exists() implies identifier.where(system='urn:oid:2.16.756.5.30.1.123.100.2.1.1').value.matches('^[A-Z][0-9]{6}$').allTrue()}ch-elm-practioner-zsr-check-digit:invalid ZSR number, cannot be processed, must pass the modulus 26 check - https://confluence.sasis.ch/display/PublicZSR/ZSR+Webservice+FAQ {identifier.where(system='urn:oid:2.16.756.5.30.1.123.100.2.1.1').exists() implies identifier.where(system='urn:oid:2.16.756.5.30.1.123.100.2.1.1').value.select(((substring(1,1).toInteger()*6)+(substring(2,1).toInteger()*5)+(substring(3,1).toInteger()*4)+(substring(4,1).toInteger()*3)+(substring(5,1).toInteger()*2)+(substring(6,1).toInteger()))mod(26)=iif(substring(0,1)='A',1,iif(substring(0,1)='B',2,iif(substring(0,1)='C',3,iif(substring(0,1)='D',4,iif(substring(0,1)='E',5,iif(substring(0,1)='F',6,iif(substring(0,1)='G',7,iif(substring(0,1)='H',8,iif(substring(0,1)='I',9,iif(substring(0,1)='J',10,iif(substring(0,1)='K',11,iif(substring(0,1)='L',12,iif(substring(0,1)='M',13,iif(substring(0,1)='N',14,iif(substring(0,1)='O',15,iif(substring(0,1)='P',16,iif(substring(0,1)='Q',17,iif(substring(0,1)='R',18,iif(substring(0,1)='S',19,iif(substring(0,1)='T',20,iif(substring(0,1)='U',21,iif(substring(0,1)='V',22,iif(substring(0,1)='W',23,iif(substring(0,1)='X',24,iif(substring(0,1)='Y',25,iif(substring(0,1)='Z',26,-1))))))))))))))))))))))))))).allTrue()}</t>
   </si>
   <si>
     <t>PRD (as one example)</t>
@@ -370,7 +370,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -791,7 +791,7 @@
     <t>dataabsentreason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {data-absent-reason}
+    <t xml:space="preserve">Extension {data-absent-reason|5.3.0}
 </t>
   </si>
   <si>
@@ -914,7 +914,7 @@
     <t>salutationandtitle</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-EN-qualifier|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-EN-qualifier|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -1766,7 +1766,7 @@
     <t>streetName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-streetName|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-ADXP-streetName|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -1788,7 +1788,7 @@
     <t>houseNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-houseNumber|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-ADXP-houseNumber|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -1810,7 +1810,7 @@
     <t>unitID</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-unitID|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-ADXP-unitID|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -1859,7 +1859,7 @@
     <t>postOfficeBoxNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-ADXP-postBox|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-ADXP-postBox|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -2066,7 +2066,7 @@
     <t>countrycode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-SC-coding|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-codedString|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -2293,7 +2293,7 @@
     <t>Practitioner.qualification.issuer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -6762,7 +6762,7 @@
         <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>140</v>
@@ -16072,7 +16072,7 @@
         <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>140</v>
@@ -16189,7 +16189,7 @@
         <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>140</v>
@@ -16306,7 +16306,7 @@
         <v>81</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>140</v>
@@ -17117,7 +17117,7 @@
         <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>140</v>
@@ -18616,7 +18616,7 @@
         <v>81</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>79</v>
+        <v>241</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>662</v>

--- a/ig/ch-elm/StructureDefinition-ch-elm-practitioner-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-practitioner-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-practitioner-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-practitioner-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-practitioner-orderer.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-practitioner-orderer.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
